--- a/public/exports-from-60-with-coowners/29188416.xlsx
+++ b/public/exports-from-60-with-coowners/29188416.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29188416.xlsx
+++ b/public/exports-from-60-with-coowners/29188416.xlsx
@@ -4039,12 +4039,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131902</t>
+          <t xml:space="preserve">311131904</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M54" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29188416.xlsx
+++ b/public/exports-from-60-with-coowners/29188416.xlsx
@@ -4039,12 +4039,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131904</t>
+          <t xml:space="preserve">311131902</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
